--- a/questions_11.xlsx
+++ b/questions_11.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="102">
   <si>
     <t>question</t>
   </si>
@@ -47,274 +47,289 @@
     <t>शक्ति</t>
   </si>
   <si>
-    <t>वेग</t>
-  </si>
-  <si>
-    <t>त्वरण</t>
-  </si>
-  <si>
     <t>बल</t>
   </si>
   <si>
-    <t>संवेग</t>
-  </si>
-  <si>
     <t>कार्य</t>
   </si>
   <si>
-    <t>कार्य का SI मात्रक क्या है?</t>
-  </si>
-  <si>
-    <t>वाट</t>
-  </si>
-  <si>
-    <t>जूल</t>
-  </si>
-  <si>
-    <t>न्यूटन</t>
-  </si>
-  <si>
-    <t>पास्कल</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
-    <t>बल और विस्थापन के बीच का कोण कितना होने पर किया गया कार्य शून्य होता है?</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>45°</t>
-  </si>
-  <si>
-    <t>90°</t>
-  </si>
-  <si>
-    <t>180°</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
-    <t>निम्नलिखित में से कौन-सी एक अदिश राशि है?</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>यदि किसी गतिमान वस्तु का वेग दोगुना कर दिया जाए, तो उसकी गतिज ऊर्जा हो जाएगी:</t>
-  </si>
-  <si>
-    <t>दोगुनी</t>
-  </si>
-  <si>
-    <t>आधी</t>
-  </si>
-  <si>
-    <t>चार गुनी</t>
-  </si>
-  <si>
-    <t>अपरिवर्तित</t>
-  </si>
-  <si>
-    <t>कार्य का विमीय सूत्र क्या है?</t>
-  </si>
-  <si>
     <t>[MLT⁻²]</t>
   </si>
   <si>
     <t>[ML²T⁻²]</t>
   </si>
   <si>
-    <t>[ML²T⁻³]</t>
-  </si>
-  <si>
-    <t>[M⁻¹L²T⁻²]</t>
-  </si>
-  <si>
-    <t>एक अश्वशक्ति (Horsepower) लगभग किसके बराबर होती है?</t>
-  </si>
-  <si>
-    <t>500 W</t>
-  </si>
-  <si>
-    <t>746 W</t>
-  </si>
-  <si>
-    <t>1000 W</t>
-  </si>
-  <si>
-    <t>60 W</t>
-  </si>
-  <si>
-    <t>किसी खुरदरी क्षैतिज सतह पर फिसलती वस्तु पर घर्षण बल द्वारा किया गया कार्य होता है:</t>
-  </si>
-  <si>
-    <t>धनात्मक</t>
-  </si>
-  <si>
-    <t>ऋणात्मक</t>
-  </si>
-  <si>
     <t>शून्य</t>
   </si>
   <si>
-    <t>अनंत</t>
-  </si>
-  <si>
-    <t>कार्य-ऊर्जा प्रमेय के अनुसार, किसी कण पर सभी बलों द्वारा किया गया कुल कार्य किसके बराबर होता है?</t>
-  </si>
-  <si>
-    <t>स्थितिज ऊर्जा में परिवर्तन</t>
-  </si>
-  <si>
-    <t>गतिज ऊर्जा में परिवर्तन</t>
-  </si>
-  <si>
-    <t>कुल यांत्रिक ऊर्जा</t>
-  </si>
-  <si>
-    <t>संवेग परिवर्तन की दर</t>
-  </si>
-  <si>
-    <t>2 kg द्रव्यमान की एक वस्तु को 5 m की ऊँचाई तक उठाया जाता है (g = 9.8 m/s²)। गुरुत्वाकर्षण के विरुद्ध किया गया कार्य होगा:</t>
-  </si>
-  <si>
-    <t>98 J</t>
-  </si>
-  <si>
-    <t>49 J</t>
-  </si>
-  <si>
-    <t>196 J</t>
-  </si>
-  <si>
-    <t>10 J</t>
-  </si>
-  <si>
-    <t>1 किलोवाट-घंटा (kWh) का मान जूल में कितना होता है?</t>
-  </si>
-  <si>
-    <t>3.6 × 10⁵ J</t>
-  </si>
-  <si>
-    <t>3.6 × 10⁶ J</t>
-  </si>
-  <si>
-    <t>1000 J</t>
-  </si>
-  <si>
-    <t>3600 J</t>
-  </si>
-  <si>
-    <t>एक संरक्षी बल क्षेत्र में किसी बंद पथ के अनुदिश वस्तु को ले जाने में किया गया कार्य होता है:</t>
-  </si>
-  <si>
-    <t>निम्नलिखित में से कौन-सा बल एक असंरक्षी (non-conservative) बल है?</t>
-  </si>
-  <si>
-    <t>गुरुत्वाकर्षण बल</t>
-  </si>
-  <si>
-    <t>स्थिरवैद्युत बल</t>
-  </si>
-  <si>
-    <t>कमानी (स्प्रिंग) बल</t>
-  </si>
-  <si>
-    <t>घर्षण बल</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>x दूरी तक खिंची हुई स्प्रिंग की प्रत्यास्थ स्थितिज ऊर्जा का सूत्र क्या है?</t>
-  </si>
-  <si>
-    <t>kx</t>
-  </si>
-  <si>
-    <t>(1/2)kx²</t>
-  </si>
-  <si>
-    <t>(1/2)kx</t>
-  </si>
-  <si>
-    <t>kx²</t>
-  </si>
-  <si>
-    <t>पूर्णतः प्रत्यास्थ टक्कर में निम्नलिखित में से क्या संरक्षित रहता है?</t>
-  </si>
-  <si>
-    <t>केवल संवेग</t>
-  </si>
-  <si>
-    <t>केवल गतिज ऊर्जा</t>
-  </si>
-  <si>
-    <t>संवेग और गतिज ऊर्जा दोनों</t>
-  </si>
-  <si>
-    <t>न संवेग न गतिज ऊर्जा</t>
-  </si>
-  <si>
-    <t>शक्ति (Power) की सही परिभाषा क्या है?</t>
-  </si>
-  <si>
-    <t>बल × विस्थापन</t>
-  </si>
-  <si>
-    <t>कार्य करने की दर</t>
-  </si>
-  <si>
-    <t>कार्य × समय</t>
-  </si>
-  <si>
-    <t>बल / समय</t>
-  </si>
-  <si>
-    <t>एकसमान वृत्तीय गति में अभिकेन्द्रीय बल (centripetal force) द्वारा किया गया कार्य होता है:</t>
-  </si>
-  <si>
-    <t>सदैव धनात्मक</t>
-  </si>
-  <si>
-    <t>सदैव ऋणात्मक</t>
-  </si>
-  <si>
-    <t>सदैव शून्य</t>
-  </si>
-  <si>
-    <t>त्रिज्या पर निर्भर</t>
-  </si>
-  <si>
-    <t>पूर्णतः प्रत्यास्थ टक्कर के लिए प्रत्यावस्थान गुणांक (e) का मान क्या होता है?</t>
-  </si>
-  <si>
-    <t>0 और 1 के बीच</t>
-  </si>
-  <si>
-    <t>यदि किसी वस्तु का रेखीय संवेग 100% बढ़ा दिया जाए, तो उसकी गतिज ऊर्जा में कितने प्रतिशत की वृद्धि होगी?</t>
-  </si>
-  <si>
-    <t>स्थितिज ऊर्जा को केवल किस प्रकार के बलों के लिए परिभाषित किया जा सकता है?</t>
-  </si>
-  <si>
-    <t>संरक्षी बल</t>
-  </si>
-  <si>
-    <t>असंरक्षी बल</t>
-  </si>
-  <si>
-    <t>किसी भी बल के लिए</t>
-  </si>
-  <si>
-    <t>बल सदिश और वेग सदिश का अदिश गुणनफल (Dot Product) क्या दर्शाता है?</t>
-  </si>
-  <si>
-    <t>आघूर्ण (टॉर्क)</t>
+    <t>समय के साथ बढ़ता है</t>
+  </si>
+  <si>
+    <t>समय के साथ घटता है</t>
+  </si>
+  <si>
+    <t>शून्य ही होना चाहिए</t>
+  </si>
+  <si>
+    <t>रेखीय संवेग</t>
+  </si>
+  <si>
+    <t>गतिज ऊर्जा</t>
+  </si>
+  <si>
+    <t>कोणीय संवेग (L) और जड़त्व आघूर्ण (I) के बीच सही संबंध क्या है?</t>
+  </si>
+  <si>
+    <t>3D ठोस वस्तुओं के लिए</t>
+  </si>
+  <si>
+    <t>केवल गोलों के लिए</t>
+  </si>
+  <si>
+    <t>सभी प्रकार की वस्तुओं के लिए</t>
+  </si>
+  <si>
+    <t>बढ़ता है</t>
+  </si>
+  <si>
+    <t>घटता है</t>
+  </si>
+  <si>
+    <t>शून्य हो जाता है</t>
+  </si>
+  <si>
+    <t>अपरिवर्तित रहता है</t>
+  </si>
+  <si>
+    <t>ऊर्जा</t>
+  </si>
+  <si>
+    <t>हमेशा वस्तु के बाहर होता है</t>
+  </si>
+  <si>
+    <t>किसी निकाय पर बाह्य बल शून्य होने पर उसके द्रव्यमान केंद्र का वेग:</t>
+  </si>
+  <si>
+    <t>नियत रहता है</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण और कोणीय त्वरण के बीच सही संबंध क्या है?</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण = जड़त्व आघूर्ण / कोणीय त्वरण</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण = जड़त्व आघूर्ण × कोणीय त्वरण</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण = जड़त्व आघूर्ण × (कोणीय त्वरण)²</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण = कोणीय त्वरण / जड़त्व आघूर्ण</t>
+  </si>
+  <si>
+    <t>जड़त्व आघूर्ण का SI मात्रक क्या होता है?</t>
+  </si>
+  <si>
+    <t>किग्रा-मीटर</t>
+  </si>
+  <si>
+    <t>किग्रा-मीटर²</t>
+  </si>
+  <si>
+    <t>किग्रा/मीटर²</t>
+  </si>
+  <si>
+    <t>न्यूटन-मीटर</t>
+  </si>
+  <si>
+    <t>M द्रव्यमान और R त्रिज्या वाली वृत्ताकार वलय का केंद्रीय अक्ष के परितः जड़त्व आघूर्ण है:</t>
+  </si>
+  <si>
+    <t>(1/2)MR²</t>
+  </si>
+  <si>
+    <t>MR²</t>
+  </si>
+  <si>
+    <t>(2/5)MR²</t>
+  </si>
+  <si>
+    <t>(1/4)MR²</t>
+  </si>
+  <si>
+    <t>समान द्रव्यमान M और त्रिज्या R वाली ठोस चकती का केंद्रीय अक्ष के परितः जड़त्व आघूर्ण होता है:</t>
+  </si>
+  <si>
+    <t>(2/3)MR²</t>
+  </si>
+  <si>
+    <t>एक ठोस गोले का उसके व्यास के परितः जड़त्व आघूर्ण कितना होता है?</t>
+  </si>
+  <si>
+    <t>यदि किसी घूर्णन करते निकाय पर कोई बाह्य बल आघूर्ण न लगे, तो कौन-सी राशि संरक्षित रहती है?</t>
+  </si>
+  <si>
+    <t>कोणीय संवेग</t>
+  </si>
+  <si>
+    <t>L = Iω²</t>
+  </si>
+  <si>
+    <t>L = Iω</t>
+  </si>
+  <si>
+    <t>L = I/ω</t>
+  </si>
+  <si>
+    <t>L = (1/2)Iω</t>
+  </si>
+  <si>
+    <t>समानांतर अक्षों के प्रमेय का सही सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>I = Icm - Md²</t>
+  </si>
+  <si>
+    <t>I = Icm + Md²</t>
+  </si>
+  <si>
+    <t>I = Icm + Md</t>
+  </si>
+  <si>
+    <t>I = Icm / Md²</t>
+  </si>
+  <si>
+    <t>लम्बवत अक्षों का प्रमेय केवल किन वस्तुओं के लिए लागू होता है?</t>
+  </si>
+  <si>
+    <t>समतलीय (2D) पटल के लिए</t>
+  </si>
+  <si>
+    <t>शुद्ध लोटनी गति में जमीन के संपर्क बिंदु का तात्क्षणिक वेग कितना होता है?</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>2v</t>
+  </si>
+  <si>
+    <t>v/2</t>
+  </si>
+  <si>
+    <t>बिना फिसले लुढ़कती वस्तु की कुल गतिज ऊर्जा का सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>(1/2)Mv²</t>
+  </si>
+  <si>
+    <t>(1/2)Iω²</t>
+  </si>
+  <si>
+    <t>(1/2)Mv² + (1/2)Iω²</t>
+  </si>
+  <si>
+    <t>Mv² + Iω²</t>
+  </si>
+  <si>
+    <t>रेखीय वेग (v) और कोणीय वेग (ω) के बीच सही संबंध क्या है?</t>
+  </si>
+  <si>
+    <t>v = ω × r</t>
+  </si>
+  <si>
+    <t>v = r × ω</t>
+  </si>
+  <si>
+    <t>v = ω . r</t>
+  </si>
+  <si>
+    <t>v = ω / r</t>
+  </si>
+  <si>
+    <t>घूर्णन त्रिज्या (k) और जड़त्व आघूर्ण (I) में क्या संबंध है?</t>
+  </si>
+  <si>
+    <t>I = M / k²</t>
+  </si>
+  <si>
+    <t>I = Mk²</t>
+  </si>
+  <si>
+    <t>I = Mk</t>
+  </si>
+  <si>
+    <t>I = √(Mk)</t>
+  </si>
+  <si>
+    <t>जब कोई तैराक ऊँचाई से पानी में कूदते समय शरीर को मोड़ लेता है, तो उसका जड़त्व आघूर्ण:</t>
+  </si>
+  <si>
+    <t>L लम्बाई और M द्रव्यमान की पतली छड़ का मध्य बिंदु के लम्बवत अक्ष के परितः जड़त्व आघूर्ण है:</t>
+  </si>
+  <si>
+    <t>(1/3)ML²</t>
+  </si>
+  <si>
+    <t>(1/12)ML²</t>
+  </si>
+  <si>
+    <t>(1/2)ML²</t>
+  </si>
+  <si>
+    <t>(2/5)ML²</t>
+  </si>
+  <si>
+    <t>नत समतल पर बिना फिसले नीचे लुढ़कते समय किस वस्तु का त्वरण सबसे अधिक होगा?</t>
+  </si>
+  <si>
+    <t>वलय</t>
+  </si>
+  <si>
+    <t>ठोस चकती</t>
+  </si>
+  <si>
+    <t>ठोस गोला</t>
+  </si>
+  <si>
+    <t>खोखला गोला</t>
+  </si>
+  <si>
+    <t>बल आघूर्ण का विमीय सूत्र क्या होता है?</t>
+  </si>
+  <si>
+    <t>[ML²T⁻¹]</t>
+  </si>
+  <si>
+    <t>[ML⁻¹T⁻²]</t>
+  </si>
+  <si>
+    <t>कोणीय संवेग की विमाएँ निम्नलिखित में से किसके समान होती हैं?</t>
+  </si>
+  <si>
+    <t>प्लांक नियतांक</t>
+  </si>
+  <si>
+    <t>किसी वस्तु का द्रव्यमान केंद्र:</t>
+  </si>
+  <si>
+    <t>हमेशा वस्तु के अंदर होता है</t>
+  </si>
+  <si>
+    <t>वस्तु के अंदर या बाहर कहीं भी हो सकता है</t>
+  </si>
+  <si>
+    <t>हमेशा उसकी सतह पर होता है</t>
   </si>
 </sst>
 </file>
@@ -379,19 +394,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -696,307 +705,307 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
@@ -1013,87 +1022,87 @@
         <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="3">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1</v>
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>3</v>
-      </c>
-      <c r="E19" s="4">
-        <v>4</v>
+        <v>93</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
